--- a/public/informes-templates/INFORME SUMINISTRO.xlsx
+++ b/public/informes-templates/INFORME SUMINISTRO.xlsx
@@ -1,49 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SIP-APP\SIPAPP-HUAQUIAN\Frontend\public\informes-templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAFEC9A-FF82-49DE-97E5-AF0D6A8C8470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB53225-1165-489B-8B1E-B5DA3D85F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="GZiBxVsolQwBXQW2WOc9TYQDpmgheF2L4vj5xeQ9F4s="/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Hoja 1'!$A$1:$F$58</definedName>
+  </definedNames>
+  <calcPr calcId="171027"/>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -134,11 +105,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,6 +156,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -363,10 +341,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+  <cellXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -379,23 +355,80 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -403,71 +436,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,68 +483,53 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -752,20 +734,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:X197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="18.5" customWidth="1"/>
+    <col min="1" max="6" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -785,13 +767,13 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="27"/>
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="24"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -811,17 +793,15 @@
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
     </row>
-    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B3" s="22"/>
+    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -841,15 +821,15 @@
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
     </row>
-    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
-      <c r="B4" s="25"/>
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -869,15 +849,15 @@
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
     </row>
-    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23"/>
-      <c r="B5" s="25"/>
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -897,15 +877,15 @@
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
     </row>
-    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
-      <c r="B6" s="25"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="22"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -925,15 +905,15 @@
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
     </row>
-    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="22"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -953,15 +933,15 @@
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
     </row>
-    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
-      <c r="B8" s="25"/>
+    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="21"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -981,15 +961,15 @@
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
     </row>
-    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
+    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1009,15 +989,15 @@
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
     </row>
-    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
-      <c r="B10" s="25"/>
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="22"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1037,15 +1017,15 @@
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
     </row>
-    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="25"/>
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="31"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1065,13 +1045,13 @@
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
     </row>
-    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="32"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1091,15 +1071,15 @@
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
     </row>
-    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="12"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="31"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1119,15 +1099,15 @@
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
     </row>
-    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="19" t="s">
+      <c r="B14" s="31"/>
+      <c r="C14" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="12"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1153,11 +1133,11 @@
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
     </row>
-    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="31"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="12"/>
+    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="29"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="31"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="1"/>
@@ -1179,13 +1159,13 @@
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
     </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="34"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1205,13 +1185,13 @@
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
     </row>
-    <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
+    <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1231,13 +1211,13 @@
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
     </row>
-    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="25"/>
+    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1257,13 +1237,13 @@
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
     </row>
-    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="25"/>
+    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1283,13 +1263,13 @@
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
     </row>
-    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
+    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1309,13 +1289,13 @@
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
     </row>
-    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
+    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1335,13 +1315,13 @@
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
     </row>
-    <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
+    <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1361,13 +1341,13 @@
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
     </row>
-    <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
+    <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1387,13 +1367,13 @@
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
     </row>
-    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="25"/>
+    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -1413,13 +1393,13 @@
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
     </row>
-    <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
+    <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1439,13 +1419,13 @@
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
     </row>
-    <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
+    <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="10"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1465,13 +1445,13 @@
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
     </row>
-    <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
+    <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1491,13 +1471,13 @@
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
     </row>
-    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
+    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="10"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1517,13 +1497,13 @@
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
     </row>
-    <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
+    <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="10"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1543,13 +1523,13 @@
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
     </row>
-    <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="25"/>
+    <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1569,13 +1549,13 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
     </row>
-    <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="25"/>
+    <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1595,13 +1575,13 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
     </row>
-    <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="25"/>
+    <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1621,13 +1601,13 @@
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
     </row>
-    <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="25"/>
+    <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="10"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1647,13 +1627,13 @@
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
     </row>
-    <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="25"/>
+    <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="10"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1673,13 +1653,13 @@
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
     </row>
-    <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="25"/>
+    <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="10"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1699,13 +1679,13 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
     </row>
-    <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="25"/>
+    <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="10"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1725,13 +1705,13 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
     </row>
-    <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="25"/>
+    <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="10"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1751,13 +1731,13 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
     </row>
-    <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="25"/>
+    <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="10"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1777,13 +1757,13 @@
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
     </row>
-    <row r="39" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="25"/>
+    <row r="39" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="10"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1803,13 +1783,13 @@
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
     </row>
-    <row r="40" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="25"/>
+    <row r="40" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="10"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1829,13 +1809,13 @@
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
     </row>
-    <row r="41" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A41" s="23"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="25"/>
+    <row r="41" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="10"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1855,13 +1835,13 @@
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
     </row>
-    <row r="42" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="25"/>
+    <row r="42" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="10"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1881,13 +1861,13 @@
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
     </row>
-    <row r="43" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="26"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="27"/>
+    <row r="43" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="11"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1907,15 +1887,15 @@
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
     </row>
-    <row r="44" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="12"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="31"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1935,15 +1915,15 @@
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
     </row>
-    <row r="45" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A45" s="10" t="s">
+    <row r="45" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="12"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="31"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1963,17 +1943,17 @@
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
     </row>
-    <row r="46" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="5" t="s">
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="1"/>
@@ -1995,17 +1975,17 @@
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
     </row>
-    <row r="47" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A47" s="6">
+    <row r="47" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="15">
         <v>1</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="6"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="15"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -2025,17 +2005,17 @@
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
     </row>
-    <row r="48" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A48" s="6">
+    <row r="48" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="15">
         <v>2</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="6"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="15"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -2055,17 +2035,17 @@
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
     </row>
-    <row r="49" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A49" s="6">
+    <row r="49" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="15">
         <v>3</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="6"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="15"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -2085,17 +2065,17 @@
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
     </row>
-    <row r="50" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A50" s="6">
+    <row r="50" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="15">
         <v>4</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="6"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="15"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -2115,17 +2095,17 @@
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
     </row>
-    <row r="51" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="6">
+    <row r="51" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="15">
         <v>5</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="6"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="15"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -2145,17 +2125,17 @@
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
     </row>
-    <row r="52" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A52" s="6">
+    <row r="52" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
         <v>6</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="6"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="15"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -2175,17 +2155,17 @@
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
     </row>
-    <row r="53" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A53" s="6">
+    <row r="53" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
         <v>7</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="6"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="15"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -2205,15 +2185,15 @@
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
     </row>
-    <row r="54" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A54" s="28" t="s">
+    <row r="54" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="22"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="21"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -2233,13 +2213,13 @@
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
     </row>
-    <row r="55" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A55" s="29"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="22"/>
+    <row r="55" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="40"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="21"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -2259,13 +2239,13 @@
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
     </row>
-    <row r="56" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="12"/>
+    <row r="56" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="41"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="31"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -2285,13 +2265,13 @@
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
     </row>
-    <row r="57" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A57" s="7"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="9"/>
+    <row r="57" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="16"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="18"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -2311,13 +2291,13 @@
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
     </row>
-    <row r="58" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="12"/>
+    <row r="58" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="41"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="31"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -2337,7 +2317,7 @@
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
     </row>
-    <row r="59" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2363,7 +2343,7 @@
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
     </row>
-    <row r="60" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2389,7 +2369,7 @@
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
     </row>
-    <row r="61" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2415,7 +2395,7 @@
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
     </row>
-    <row r="62" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2441,7 +2421,7 @@
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
     </row>
-    <row r="63" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2467,7 +2447,7 @@
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
     </row>
-    <row r="64" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2493,7 +2473,7 @@
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
     </row>
-    <row r="65" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2519,7 +2499,7 @@
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
     </row>
-    <row r="66" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2545,7 +2525,7 @@
       <c r="W66" s="1"/>
       <c r="X66" s="1"/>
     </row>
-    <row r="67" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2571,7 +2551,7 @@
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
     </row>
-    <row r="68" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2597,7 +2577,7 @@
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
     </row>
-    <row r="69" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2623,7 +2603,7 @@
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
     </row>
-    <row r="70" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2649,7 +2629,7 @@
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
     </row>
-    <row r="71" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2675,7 +2655,7 @@
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
     </row>
-    <row r="72" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2701,7 +2681,7 @@
       <c r="W72" s="1"/>
       <c r="X72" s="1"/>
     </row>
-    <row r="73" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2727,7 +2707,7 @@
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
     </row>
-    <row r="74" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2753,7 +2733,7 @@
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
     </row>
-    <row r="75" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2779,7 +2759,7 @@
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
     </row>
-    <row r="76" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2805,7 +2785,7 @@
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
     </row>
-    <row r="77" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2831,7 +2811,7 @@
       <c r="W77" s="1"/>
       <c r="X77" s="1"/>
     </row>
-    <row r="78" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2857,7 +2837,7 @@
       <c r="W78" s="1"/>
       <c r="X78" s="1"/>
     </row>
-    <row r="79" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2883,7 +2863,7 @@
       <c r="W79" s="1"/>
       <c r="X79" s="1"/>
     </row>
-    <row r="80" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2909,7 +2889,7 @@
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
     </row>
-    <row r="81" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2935,7 +2915,7 @@
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
     </row>
-    <row r="82" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2961,7 +2941,7 @@
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
     </row>
-    <row r="83" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2987,7 +2967,7 @@
       <c r="W83" s="1"/>
       <c r="X83" s="1"/>
     </row>
-    <row r="84" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3013,7 +2993,7 @@
       <c r="W84" s="1"/>
       <c r="X84" s="1"/>
     </row>
-    <row r="85" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3039,7 +3019,7 @@
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
     </row>
-    <row r="86" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3065,7 +3045,7 @@
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
     </row>
-    <row r="87" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3091,7 +3071,7 @@
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
     </row>
-    <row r="88" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3117,7 +3097,7 @@
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
     </row>
-    <row r="89" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3143,7 +3123,7 @@
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
     </row>
-    <row r="90" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3169,7 +3149,7 @@
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
     </row>
-    <row r="91" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3195,7 +3175,7 @@
       <c r="W91" s="1"/>
       <c r="X91" s="1"/>
     </row>
-    <row r="92" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3221,7 +3201,7 @@
       <c r="W92" s="1"/>
       <c r="X92" s="1"/>
     </row>
-    <row r="93" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3247,7 +3227,7 @@
       <c r="W93" s="1"/>
       <c r="X93" s="1"/>
     </row>
-    <row r="94" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3273,7 +3253,7 @@
       <c r="W94" s="1"/>
       <c r="X94" s="1"/>
     </row>
-    <row r="95" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3299,7 +3279,7 @@
       <c r="W95" s="1"/>
       <c r="X95" s="1"/>
     </row>
-    <row r="96" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3325,7 +3305,7 @@
       <c r="W96" s="1"/>
       <c r="X96" s="1"/>
     </row>
-    <row r="97" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3351,7 +3331,7 @@
       <c r="W97" s="1"/>
       <c r="X97" s="1"/>
     </row>
-    <row r="98" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3377,7 +3357,7 @@
       <c r="W98" s="1"/>
       <c r="X98" s="1"/>
     </row>
-    <row r="99" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3403,7 +3383,7 @@
       <c r="W99" s="1"/>
       <c r="X99" s="1"/>
     </row>
-    <row r="100" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3429,7 +3409,7 @@
       <c r="W100" s="1"/>
       <c r="X100" s="1"/>
     </row>
-    <row r="101" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3455,7 +3435,7 @@
       <c r="W101" s="1"/>
       <c r="X101" s="1"/>
     </row>
-    <row r="102" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3481,7 +3461,7 @@
       <c r="W102" s="1"/>
       <c r="X102" s="1"/>
     </row>
-    <row r="103" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3507,7 +3487,7 @@
       <c r="W103" s="1"/>
       <c r="X103" s="1"/>
     </row>
-    <row r="104" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3533,7 +3513,7 @@
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
     </row>
-    <row r="105" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3559,7 +3539,7 @@
       <c r="W105" s="1"/>
       <c r="X105" s="1"/>
     </row>
-    <row r="106" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3585,7 +3565,7 @@
       <c r="W106" s="1"/>
       <c r="X106" s="1"/>
     </row>
-    <row r="107" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3611,7 +3591,7 @@
       <c r="W107" s="1"/>
       <c r="X107" s="1"/>
     </row>
-    <row r="108" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3637,7 +3617,7 @@
       <c r="W108" s="1"/>
       <c r="X108" s="1"/>
     </row>
-    <row r="109" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3663,7 +3643,7 @@
       <c r="W109" s="1"/>
       <c r="X109" s="1"/>
     </row>
-    <row r="110" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3689,7 +3669,7 @@
       <c r="W110" s="1"/>
       <c r="X110" s="1"/>
     </row>
-    <row r="111" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3715,7 +3695,7 @@
       <c r="W111" s="1"/>
       <c r="X111" s="1"/>
     </row>
-    <row r="112" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3741,7 +3721,7 @@
       <c r="W112" s="1"/>
       <c r="X112" s="1"/>
     </row>
-    <row r="113" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3767,7 +3747,7 @@
       <c r="W113" s="1"/>
       <c r="X113" s="1"/>
     </row>
-    <row r="114" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3793,7 +3773,7 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
     </row>
-    <row r="115" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3819,7 +3799,7 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
     </row>
-    <row r="116" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3845,7 +3825,7 @@
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
     </row>
-    <row r="117" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3871,7 +3851,7 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
     </row>
-    <row r="118" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3897,7 +3877,7 @@
       <c r="W118" s="1"/>
       <c r="X118" s="1"/>
     </row>
-    <row r="119" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3923,7 +3903,7 @@
       <c r="W119" s="1"/>
       <c r="X119" s="1"/>
     </row>
-    <row r="120" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3949,7 +3929,7 @@
       <c r="W120" s="1"/>
       <c r="X120" s="1"/>
     </row>
-    <row r="121" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3975,7 +3955,7 @@
       <c r="W121" s="1"/>
       <c r="X121" s="1"/>
     </row>
-    <row r="122" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4001,7 +3981,7 @@
       <c r="W122" s="1"/>
       <c r="X122" s="1"/>
     </row>
-    <row r="123" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4027,7 +4007,7 @@
       <c r="W123" s="1"/>
       <c r="X123" s="1"/>
     </row>
-    <row r="124" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4053,7 +4033,7 @@
       <c r="W124" s="1"/>
       <c r="X124" s="1"/>
     </row>
-    <row r="125" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4079,7 +4059,7 @@
       <c r="W125" s="1"/>
       <c r="X125" s="1"/>
     </row>
-    <row r="126" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4105,7 +4085,7 @@
       <c r="W126" s="1"/>
       <c r="X126" s="1"/>
     </row>
-    <row r="127" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4131,7 +4111,7 @@
       <c r="W127" s="1"/>
       <c r="X127" s="1"/>
     </row>
-    <row r="128" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4157,7 +4137,7 @@
       <c r="W128" s="1"/>
       <c r="X128" s="1"/>
     </row>
-    <row r="129" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4183,7 +4163,7 @@
       <c r="W129" s="1"/>
       <c r="X129" s="1"/>
     </row>
-    <row r="130" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4209,7 +4189,7 @@
       <c r="W130" s="1"/>
       <c r="X130" s="1"/>
     </row>
-    <row r="131" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4235,7 +4215,7 @@
       <c r="W131" s="1"/>
       <c r="X131" s="1"/>
     </row>
-    <row r="132" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4261,7 +4241,7 @@
       <c r="W132" s="1"/>
       <c r="X132" s="1"/>
     </row>
-    <row r="133" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4287,7 +4267,7 @@
       <c r="W133" s="1"/>
       <c r="X133" s="1"/>
     </row>
-    <row r="134" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4313,7 +4293,7 @@
       <c r="W134" s="1"/>
       <c r="X134" s="1"/>
     </row>
-    <row r="135" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4339,7 +4319,7 @@
       <c r="W135" s="1"/>
       <c r="X135" s="1"/>
     </row>
-    <row r="136" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4365,7 +4345,7 @@
       <c r="W136" s="1"/>
       <c r="X136" s="1"/>
     </row>
-    <row r="137" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4391,7 +4371,7 @@
       <c r="W137" s="1"/>
       <c r="X137" s="1"/>
     </row>
-    <row r="138" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4417,7 +4397,7 @@
       <c r="W138" s="1"/>
       <c r="X138" s="1"/>
     </row>
-    <row r="139" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4443,7 +4423,7 @@
       <c r="W139" s="1"/>
       <c r="X139" s="1"/>
     </row>
-    <row r="140" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4469,7 +4449,7 @@
       <c r="W140" s="1"/>
       <c r="X140" s="1"/>
     </row>
-    <row r="141" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4495,7 +4475,7 @@
       <c r="W141" s="1"/>
       <c r="X141" s="1"/>
     </row>
-    <row r="142" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4521,7 +4501,7 @@
       <c r="W142" s="1"/>
       <c r="X142" s="1"/>
     </row>
-    <row r="143" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4547,7 +4527,7 @@
       <c r="W143" s="1"/>
       <c r="X143" s="1"/>
     </row>
-    <row r="144" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4573,7 +4553,7 @@
       <c r="W144" s="1"/>
       <c r="X144" s="1"/>
     </row>
-    <row r="145" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4599,7 +4579,7 @@
       <c r="W145" s="1"/>
       <c r="X145" s="1"/>
     </row>
-    <row r="146" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4625,7 +4605,7 @@
       <c r="W146" s="1"/>
       <c r="X146" s="1"/>
     </row>
-    <row r="147" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4651,7 +4631,7 @@
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
     </row>
-    <row r="148" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4677,7 +4657,7 @@
       <c r="W148" s="1"/>
       <c r="X148" s="1"/>
     </row>
-    <row r="149" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4703,7 +4683,7 @@
       <c r="W149" s="1"/>
       <c r="X149" s="1"/>
     </row>
-    <row r="150" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4729,7 +4709,7 @@
       <c r="W150" s="1"/>
       <c r="X150" s="1"/>
     </row>
-    <row r="151" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4755,7 +4735,7 @@
       <c r="W151" s="1"/>
       <c r="X151" s="1"/>
     </row>
-    <row r="152" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4781,7 +4761,7 @@
       <c r="W152" s="1"/>
       <c r="X152" s="1"/>
     </row>
-    <row r="153" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4807,7 +4787,7 @@
       <c r="W153" s="1"/>
       <c r="X153" s="1"/>
     </row>
-    <row r="154" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4833,7 +4813,7 @@
       <c r="W154" s="1"/>
       <c r="X154" s="1"/>
     </row>
-    <row r="155" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4859,7 +4839,7 @@
       <c r="W155" s="1"/>
       <c r="X155" s="1"/>
     </row>
-    <row r="156" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4885,7 +4865,7 @@
       <c r="W156" s="1"/>
       <c r="X156" s="1"/>
     </row>
-    <row r="157" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4911,7 +4891,7 @@
       <c r="W157" s="1"/>
       <c r="X157" s="1"/>
     </row>
-    <row r="158" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4937,7 +4917,7 @@
       <c r="W158" s="1"/>
       <c r="X158" s="1"/>
     </row>
-    <row r="159" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4963,7 +4943,7 @@
       <c r="W159" s="1"/>
       <c r="X159" s="1"/>
     </row>
-    <row r="160" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4989,7 +4969,7 @@
       <c r="W160" s="1"/>
       <c r="X160" s="1"/>
     </row>
-    <row r="161" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5015,7 +4995,7 @@
       <c r="W161" s="1"/>
       <c r="X161" s="1"/>
     </row>
-    <row r="162" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5041,7 +5021,7 @@
       <c r="W162" s="1"/>
       <c r="X162" s="1"/>
     </row>
-    <row r="163" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5067,7 +5047,7 @@
       <c r="W163" s="1"/>
       <c r="X163" s="1"/>
     </row>
-    <row r="164" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5093,7 +5073,7 @@
       <c r="W164" s="1"/>
       <c r="X164" s="1"/>
     </row>
-    <row r="165" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5119,7 +5099,7 @@
       <c r="W165" s="1"/>
       <c r="X165" s="1"/>
     </row>
-    <row r="166" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5145,7 +5125,7 @@
       <c r="W166" s="1"/>
       <c r="X166" s="1"/>
     </row>
-    <row r="167" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5171,7 +5151,7 @@
       <c r="W167" s="1"/>
       <c r="X167" s="1"/>
     </row>
-    <row r="168" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5197,7 +5177,7 @@
       <c r="W168" s="1"/>
       <c r="X168" s="1"/>
     </row>
-    <row r="169" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5223,7 +5203,7 @@
       <c r="W169" s="1"/>
       <c r="X169" s="1"/>
     </row>
-    <row r="170" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5249,7 +5229,7 @@
       <c r="W170" s="1"/>
       <c r="X170" s="1"/>
     </row>
-    <row r="171" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5275,7 +5255,7 @@
       <c r="W171" s="1"/>
       <c r="X171" s="1"/>
     </row>
-    <row r="172" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5301,7 +5281,7 @@
       <c r="W172" s="1"/>
       <c r="X172" s="1"/>
     </row>
-    <row r="173" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5327,7 +5307,7 @@
       <c r="W173" s="1"/>
       <c r="X173" s="1"/>
     </row>
-    <row r="174" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5353,7 +5333,7 @@
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
     </row>
-    <row r="175" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5379,7 +5359,7 @@
       <c r="W175" s="1"/>
       <c r="X175" s="1"/>
     </row>
-    <row r="176" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5405,7 +5385,7 @@
       <c r="W176" s="1"/>
       <c r="X176" s="1"/>
     </row>
-    <row r="177" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5431,7 +5411,7 @@
       <c r="W177" s="1"/>
       <c r="X177" s="1"/>
     </row>
-    <row r="178" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5457,7 +5437,7 @@
       <c r="W178" s="1"/>
       <c r="X178" s="1"/>
     </row>
-    <row r="179" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5483,7 +5463,7 @@
       <c r="W179" s="1"/>
       <c r="X179" s="1"/>
     </row>
-    <row r="180" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5509,7 +5489,7 @@
       <c r="W180" s="1"/>
       <c r="X180" s="1"/>
     </row>
-    <row r="181" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5535,7 +5515,7 @@
       <c r="W181" s="1"/>
       <c r="X181" s="1"/>
     </row>
-    <row r="182" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5561,7 +5541,7 @@
       <c r="W182" s="1"/>
       <c r="X182" s="1"/>
     </row>
-    <row r="183" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5587,7 +5567,7 @@
       <c r="W183" s="1"/>
       <c r="X183" s="1"/>
     </row>
-    <row r="184" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5613,7 +5593,7 @@
       <c r="W184" s="1"/>
       <c r="X184" s="1"/>
     </row>
-    <row r="185" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5639,7 +5619,7 @@
       <c r="W185" s="1"/>
       <c r="X185" s="1"/>
     </row>
-    <row r="186" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5665,7 +5645,7 @@
       <c r="W186" s="1"/>
       <c r="X186" s="1"/>
     </row>
-    <row r="187" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5691,7 +5671,7 @@
       <c r="W187" s="1"/>
       <c r="X187" s="1"/>
     </row>
-    <row r="188" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5717,7 +5697,7 @@
       <c r="W188" s="1"/>
       <c r="X188" s="1"/>
     </row>
-    <row r="189" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5743,7 +5723,7 @@
       <c r="W189" s="1"/>
       <c r="X189" s="1"/>
     </row>
-    <row r="190" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5769,7 +5749,7 @@
       <c r="W190" s="1"/>
       <c r="X190" s="1"/>
     </row>
-    <row r="191" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5795,7 +5775,7 @@
       <c r="W191" s="1"/>
       <c r="X191" s="1"/>
     </row>
-    <row r="192" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5821,7 +5801,7 @@
       <c r="W192" s="1"/>
       <c r="X192" s="1"/>
     </row>
-    <row r="193" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5847,7 +5827,7 @@
       <c r="W193" s="1"/>
       <c r="X193" s="1"/>
     </row>
-    <row r="194" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5873,7 +5853,7 @@
       <c r="W194" s="1"/>
       <c r="X194" s="1"/>
     </row>
-    <row r="195" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5899,7 +5879,7 @@
       <c r="W195" s="1"/>
       <c r="X195" s="1"/>
     </row>
-    <row r="196" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5925,7 +5905,7 @@
       <c r="W196" s="1"/>
       <c r="X196" s="1"/>
     </row>
-    <row r="197" spans="1:24" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5952,43 +5932,43 @@
       <c r="X197" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="32">
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A3:B11"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A17:F43"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="92" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/public/informes-templates/INFORME SUMINISTRO.xlsx
+++ b/public/informes-templates/INFORME SUMINISTRO.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB53225-1165-489B-8B1E-B5DA3D85F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74040D07-7F98-4CBC-924B-1AD88151EFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,43 +11,19 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Hoja 1'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Hoja 1'!$A$1:$F$51</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>INFORME DE SUMINISTRO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
   <si>
-    <t>TIPO</t>
-  </si>
-  <si>
     <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>FECHA</t>
   </si>
   <si>
     <t>DATOS DEL COMPONENTE</t>
@@ -133,13 +109,6 @@
     <font>
       <b/>
       <i/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -170,8 +139,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,6 +168,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -341,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -349,53 +335,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -415,19 +362,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -436,35 +383,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,55 +452,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -733,21 +655,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X197"/>
+  <dimension ref="A1:X190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -768,12 +690,12 @@
       <c r="X1" s="1"/>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="24"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -794,14 +716,12 @@
       <c r="X2" s="1"/>
     </row>
     <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -822,14 +742,12 @@
       <c r="X3" s="1"/>
     </row>
     <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -850,14 +768,14 @@
       <c r="X4" s="1"/>
     </row>
     <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+      <c r="A5" s="16" t="s">
+        <v>2</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -878,14 +796,20 @@
       <c r="X5" s="1"/>
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="21"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -906,14 +830,12 @@
       <c r="X6" s="1"/>
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="21"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -934,14 +856,12 @@
       <c r="X7" s="1"/>
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -962,14 +882,12 @@
       <c r="X8" s="1"/>
     </row>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="30"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -990,14 +908,12 @@
       <c r="X9" s="1"/>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1018,14 +934,12 @@
       <c r="X10" s="1"/>
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1046,12 +960,12 @@
       <c r="X11" s="1"/>
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1072,14 +986,12 @@
       <c r="X12" s="1"/>
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1100,20 +1012,12 @@
       <c r="X13" s="1"/>
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A14" s="31"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1134,12 +1038,12 @@
       <c r="X14" s="1"/>
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1160,12 +1064,12 @@
       <c r="X15" s="1"/>
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1186,12 +1090,12 @@
       <c r="X16" s="1"/>
     </row>
     <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1212,12 +1116,12 @@
       <c r="X17" s="1"/>
     </row>
     <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1238,12 +1142,12 @@
       <c r="X18" s="1"/>
     </row>
     <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1264,12 +1168,12 @@
       <c r="X19" s="1"/>
     </row>
     <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="10"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1290,12 +1194,12 @@
       <c r="X20" s="1"/>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1316,12 +1220,12 @@
       <c r="X21" s="1"/>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="10"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1342,12 +1246,12 @@
       <c r="X22" s="1"/>
     </row>
     <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="10"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1368,12 +1272,12 @@
       <c r="X23" s="1"/>
     </row>
     <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="10"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -1394,12 +1298,12 @@
       <c r="X24" s="1"/>
     </row>
     <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="10"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="33"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1420,12 +1324,12 @@
       <c r="X25" s="1"/>
     </row>
     <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1446,12 +1350,12 @@
       <c r="X26" s="1"/>
     </row>
     <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1472,12 +1376,12 @@
       <c r="X27" s="1"/>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="10"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="33"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1498,12 +1402,12 @@
       <c r="X28" s="1"/>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="10"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1524,12 +1428,12 @@
       <c r="X29" s="1"/>
     </row>
     <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="10"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1549,13 +1453,13 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
     </row>
-    <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="10"/>
+    <row r="31" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="33"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1575,13 +1479,13 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
     </row>
-    <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="10"/>
+    <row r="32" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="31"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="33"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1601,13 +1505,13 @@
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
     </row>
-    <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="10"/>
+    <row r="33" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="31"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="33"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1627,13 +1531,13 @@
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
     </row>
-    <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="10"/>
+    <row r="34" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="31"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="33"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1653,13 +1557,13 @@
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
     </row>
-    <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="10"/>
+    <row r="35" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="34"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1679,13 +1583,15 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
     </row>
-    <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="10"/>
+    <row r="36" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1705,13 +1611,15 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
     </row>
-    <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="10"/>
+    <row r="37" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1731,13 +1639,19 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
     </row>
-    <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="10"/>
+    <row r="38" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1758,12 +1672,16 @@
       <c r="X38" s="1"/>
     </row>
     <row r="39" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="10"/>
+      <c r="A39" s="5">
+        <v>1</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="5"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1784,12 +1702,16 @@
       <c r="X39" s="1"/>
     </row>
     <row r="40" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="10"/>
+      <c r="A40" s="5">
+        <v>2</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="5"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1810,12 +1732,16 @@
       <c r="X40" s="1"/>
     </row>
     <row r="41" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="10"/>
+      <c r="A41" s="5">
+        <v>3</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="5"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1836,12 +1762,16 @@
       <c r="X41" s="1"/>
     </row>
     <row r="42" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="10"/>
+      <c r="A42" s="5">
+        <v>4</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="5"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1862,12 +1792,16 @@
       <c r="X42" s="1"/>
     </row>
     <row r="43" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="13"/>
+      <c r="A43" s="5">
+        <v>5</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1888,14 +1822,16 @@
       <c r="X43" s="1"/>
     </row>
     <row r="44" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
-        <v>14</v>
+      <c r="A44" s="5">
+        <v>6</v>
       </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="31"/>
+      <c r="B44" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="5"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1916,14 +1852,16 @@
       <c r="X44" s="1"/>
     </row>
     <row r="45" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="36" t="s">
-        <v>15</v>
+      <c r="A45" s="5">
+        <v>7</v>
       </c>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="31"/>
+      <c r="B45" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="5"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1944,18 +1882,14 @@
       <c r="X45" s="1"/>
     </row>
     <row r="46" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="14" t="s">
+      <c r="A46" s="25" t="s">
         <v>18</v>
       </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1976,16 +1910,12 @@
       <c r="X46" s="1"/>
     </row>
     <row r="47" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15">
-        <v>1</v>
-      </c>
-      <c r="B47" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="15"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -2006,16 +1936,12 @@
       <c r="X47" s="1"/>
     </row>
     <row r="48" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="15">
-        <v>2</v>
-      </c>
-      <c r="B48" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="15"/>
+      <c r="A48" s="27"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="18"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -2036,16 +1962,12 @@
       <c r="X48" s="1"/>
     </row>
     <row r="49" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15">
-        <v>3</v>
-      </c>
-      <c r="B49" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="15"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="18"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -2066,16 +1988,12 @@
       <c r="X49" s="1"/>
     </row>
     <row r="50" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
-        <v>4</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="15"/>
+      <c r="A50" s="27"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="18"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -2096,16 +2014,12 @@
       <c r="X50" s="1"/>
     </row>
     <row r="51" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15">
-        <v>5</v>
-      </c>
-      <c r="B51" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="15"/>
+      <c r="A51" s="27"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="18"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -2126,16 +2040,12 @@
       <c r="X51" s="1"/>
     </row>
     <row r="52" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="15">
-        <v>6</v>
-      </c>
-      <c r="B52" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="15"/>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -2156,16 +2066,12 @@
       <c r="X52" s="1"/>
     </row>
     <row r="53" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15">
-        <v>7</v>
-      </c>
-      <c r="B53" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="15"/>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -2186,14 +2092,12 @@
       <c r="X53" s="1"/>
     </row>
     <row r="54" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="21"/>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -2214,12 +2118,12 @@
       <c r="X54" s="1"/>
     </row>
     <row r="55" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="21"/>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -2240,12 +2144,12 @@
       <c r="X55" s="1"/>
     </row>
     <row r="56" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="41"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="31"/>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -2266,12 +2170,12 @@
       <c r="X56" s="1"/>
     </row>
     <row r="57" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="18"/>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -2292,12 +2196,12 @@
       <c r="X57" s="1"/>
     </row>
     <row r="58" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="41"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="31"/>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -5749,226 +5653,36 @@
       <c r="W190" s="1"/>
       <c r="X190" s="1"/>
     </row>
-    <row r="191" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="1"/>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
-      <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-      <c r="H191" s="1"/>
-      <c r="I191" s="1"/>
-      <c r="J191" s="1"/>
-      <c r="K191" s="1"/>
-      <c r="L191" s="1"/>
-      <c r="M191" s="1"/>
-      <c r="N191" s="1"/>
-      <c r="O191" s="1"/>
-      <c r="P191" s="1"/>
-      <c r="Q191" s="1"/>
-      <c r="R191" s="1"/>
-      <c r="S191" s="1"/>
-      <c r="T191" s="1"/>
-      <c r="U191" s="1"/>
-      <c r="V191" s="1"/>
-      <c r="W191" s="1"/>
-      <c r="X191" s="1"/>
-    </row>
-    <row r="192" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="1"/>
-      <c r="I192" s="1"/>
-      <c r="J192" s="1"/>
-      <c r="K192" s="1"/>
-      <c r="L192" s="1"/>
-      <c r="M192" s="1"/>
-      <c r="N192" s="1"/>
-      <c r="O192" s="1"/>
-      <c r="P192" s="1"/>
-      <c r="Q192" s="1"/>
-      <c r="R192" s="1"/>
-      <c r="S192" s="1"/>
-      <c r="T192" s="1"/>
-      <c r="U192" s="1"/>
-      <c r="V192" s="1"/>
-      <c r="W192" s="1"/>
-      <c r="X192" s="1"/>
-    </row>
-    <row r="193" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="1"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
-      <c r="E193" s="1"/>
-      <c r="F193" s="1"/>
-      <c r="G193" s="1"/>
-      <c r="H193" s="1"/>
-      <c r="I193" s="1"/>
-      <c r="J193" s="1"/>
-      <c r="K193" s="1"/>
-      <c r="L193" s="1"/>
-      <c r="M193" s="1"/>
-      <c r="N193" s="1"/>
-      <c r="O193" s="1"/>
-      <c r="P193" s="1"/>
-      <c r="Q193" s="1"/>
-      <c r="R193" s="1"/>
-      <c r="S193" s="1"/>
-      <c r="T193" s="1"/>
-      <c r="U193" s="1"/>
-      <c r="V193" s="1"/>
-      <c r="W193" s="1"/>
-      <c r="X193" s="1"/>
-    </row>
-    <row r="194" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
-      <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
-      <c r="H194" s="1"/>
-      <c r="I194" s="1"/>
-      <c r="J194" s="1"/>
-      <c r="K194" s="1"/>
-      <c r="L194" s="1"/>
-      <c r="M194" s="1"/>
-      <c r="N194" s="1"/>
-      <c r="O194" s="1"/>
-      <c r="P194" s="1"/>
-      <c r="Q194" s="1"/>
-      <c r="R194" s="1"/>
-      <c r="S194" s="1"/>
-      <c r="T194" s="1"/>
-      <c r="U194" s="1"/>
-      <c r="V194" s="1"/>
-      <c r="W194" s="1"/>
-      <c r="X194" s="1"/>
-    </row>
-    <row r="195" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="1"/>
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
-      <c r="E195" s="1"/>
-      <c r="F195" s="1"/>
-      <c r="G195" s="1"/>
-      <c r="H195" s="1"/>
-      <c r="I195" s="1"/>
-      <c r="J195" s="1"/>
-      <c r="K195" s="1"/>
-      <c r="L195" s="1"/>
-      <c r="M195" s="1"/>
-      <c r="N195" s="1"/>
-      <c r="O195" s="1"/>
-      <c r="P195" s="1"/>
-      <c r="Q195" s="1"/>
-      <c r="R195" s="1"/>
-      <c r="S195" s="1"/>
-      <c r="T195" s="1"/>
-      <c r="U195" s="1"/>
-      <c r="V195" s="1"/>
-      <c r="W195" s="1"/>
-      <c r="X195" s="1"/>
-    </row>
-    <row r="196" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="1"/>
-      <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
-      <c r="E196" s="1"/>
-      <c r="F196" s="1"/>
-      <c r="G196" s="1"/>
-      <c r="H196" s="1"/>
-      <c r="I196" s="1"/>
-      <c r="J196" s="1"/>
-      <c r="K196" s="1"/>
-      <c r="L196" s="1"/>
-      <c r="M196" s="1"/>
-      <c r="N196" s="1"/>
-      <c r="O196" s="1"/>
-      <c r="P196" s="1"/>
-      <c r="Q196" s="1"/>
-      <c r="R196" s="1"/>
-      <c r="S196" s="1"/>
-      <c r="T196" s="1"/>
-      <c r="U196" s="1"/>
-      <c r="V196" s="1"/>
-      <c r="W196" s="1"/>
-      <c r="X196" s="1"/>
-    </row>
-    <row r="197" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="1"/>
-      <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
-      <c r="E197" s="1"/>
-      <c r="F197" s="1"/>
-      <c r="G197" s="1"/>
-      <c r="H197" s="1"/>
-      <c r="I197" s="1"/>
-      <c r="J197" s="1"/>
-      <c r="K197" s="1"/>
-      <c r="L197" s="1"/>
-      <c r="M197" s="1"/>
-      <c r="N197" s="1"/>
-      <c r="O197" s="1"/>
-      <c r="P197" s="1"/>
-      <c r="Q197" s="1"/>
-      <c r="R197" s="1"/>
-      <c r="S197" s="1"/>
-      <c r="T197" s="1"/>
-      <c r="U197" s="1"/>
-      <c r="V197" s="1"/>
-      <c r="W197" s="1"/>
-      <c r="X197" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+  <mergeCells count="25">
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="92" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>